--- a/artfynd/A 29025-2024 artfynd.xlsx
+++ b/artfynd/A 29025-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126223737</v>
       </c>
       <c r="B2" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29025-2024 artfynd.xlsx
+++ b/artfynd/A 29025-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126223737</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29025-2024 artfynd.xlsx
+++ b/artfynd/A 29025-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126223737</v>
       </c>
       <c r="B2" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29025-2024 artfynd.xlsx
+++ b/artfynd/A 29025-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126223737</v>
       </c>
       <c r="B2" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
